--- a/Claude outputs/ITSM_Test_Case_Suite.xlsx
+++ b/Claude outputs/ITSM_Test_Case_Suite.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'ITSM Test Cases'!$A$1:$N$61</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'ITSM Test Cases'!$A$1:$N$72</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="311">
   <si>
     <t xml:space="preserve">Test ID</t>
   </si>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">Admin defines IT support teams (assignment groups)</t>
   </si>
   <si>
-    <t xml:space="preserve">PUT /itsm-config itsm.itGroups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Groups saved and returned by GET /itsm-config</t>
+    <t xml:space="preserve">PUT /itsm-config itsm.itGroups (legacy list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saved; teams themselves are managed in ITSM Setup</t>
   </si>
   <si>
     <t xml:space="preserve">Medium</t>
@@ -107,663 +107,786 @@
     <t xml:space="preserve">Each team lists its members so tickets can be routed to a queue and members see their queue</t>
   </si>
   <si>
+    <t xml:space="preserve">CFG-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only admin can change ITSM configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUT /itsm-config as IT Asset Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA Policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create SLA policies per priority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /sla-policies Critical 1h/4h, High 2h/8h, Medium 4h/24h, Low 8h/72h (Incident)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA policy validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /sla-policies with resolution time −5 and no name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only admin / ITSM admin can change SLA policies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /sla-policies as a user without ITSM rights (Asset Viewer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approval Workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure approval matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /approval-matrix: Change L1 Change Manager, L2 CAB; Service Request L1 Line Manager; Incident L1 IT Head for Priority:Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rules created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approval matrix is admin-only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /approval-matrix as IT Asset Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each level is linked to real approvers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read the rules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change L1 → IT Hub role "Change Manager"; L2 → named person; label shows who</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incidents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log an incident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /incidents (High, Network › VPN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 201; INC-00001; status Open; routed to Network Team; SLA due = created + 8h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory fields enforced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /incidents without title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 400 with message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid priority / status rejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /incidents priority "Urgent!!"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created-by is the signed-in user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /incidents; read createdBy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">createdBy = signed-in user (not client supplied)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign to a team member (ticket assignment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH assignedTo = Desktop engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assignee saved; history records "assigned to …"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass ticket to another team (L1 → Network Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH assignedGroup IT Helpdesk (without, then with transferReason)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason required; history records the transfer; new team emailed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assignee must be a valid user / team member</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH assignedTo "Nobody Real", assignedGroup "Ghost Team"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status transitions follow the lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open → In Progress → Resolved (with notes) → Closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each step saved; resolvedAt / closedAt set; history rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve requires resolution notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH status Resolved without notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid jump blocked (Closed → In Progress without reopen reason)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH a Closed incident to In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 400 or reopen with reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1/S1 incident is escalated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST Critical/S1 incident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status Escalated (or flag) + IT Head approval; notification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical incident gets IT Head approval step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /approvals/Incident/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Pending approval (L1 IT Head)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket numbers stay unique under parallel creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 incidents created at the same moment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All HTTP 201, unique numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulk update records history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /incidents/bulk-update status In Progress for 2 tickets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">History row per ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles &amp; Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service desk agent (non-admin, ITSM Incidents = Edit) logs and works an incident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign in as Service Desk Agent; POST /incidents; PATCH status In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 201 / 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee raises a service request / incident (self-service)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sign in as employee with Self-Service role; POST /service-requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User without ITSM access cannot read tickets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /incidents as Asset Viewer (no ITSM permission)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITSM modules can be granted in Roles &amp; Permissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check role modules list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITSM modules present (Incidents, Problems, Changes, KB, SLA, Service Requests, Approval Workflow)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete needs a reason and is audited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DELETE /incidents/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason required; audit entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audit trail names the person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read audit_logs for the incident create</t>
+  </si>
+  <si>
+    <t xml:space="preserve">performedBy = signed-in user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assignee / team is notified by email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign an incident; check email_outbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email logged for the assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLA breach is detected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Back-date an open High incident by 10h; GET /incidents and /incidents/stats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slaStatus "breached"; SLA Breached count ≥ 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INC-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First-response SLA is tracked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assign an incident (INC-05); read firstResponseAt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First-response time recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories &amp; Routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category catalog with sub-categories and team mapping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /itsm-catalog?ticketType=Service Request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories with sub-categories; each resolves to a team and days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category / sub-category validated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST SR with unknown category; with category that has sub-categories but none chosen; with wrong sub-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 400 with a clear message each time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-assigned to the mapped team; expected closure T+2 business days by default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee raises SR "Other" (no days set) and "Hardware Request › Monitor" (5 days)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team set automatically; dates = today + 2 / + 5 working days (Sat &amp; Sun skipped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitor → Desktop Support, closure 2026-11-02; Other → IT Helpdesk, closure 2026-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requester cannot assign the ticket to a person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee sends assignedTo on create; then PATCH assignedTo / status on own SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 403 each time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team member assigns to a member of the same team only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent One (IT Helpdesk) assigns SR to Agent Two (member) and to Change Manager (not a member)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member: HTTP 200 + email to assignee; non-member: HTTP 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agents outside the ticket’s team cannot work it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent One (not in Desktop Support) changes status of the Monitor SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requester can cancel own request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee PATCH status Cancelled on own SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise on behalf of someone (service desk only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent raises SR for Employee One; employee tries on behalf of Agent Two</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent: requester = Employee One and visible in the employee’s list; employee: HTTP 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin maps categories and days; new tickets follow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH catalog "Other" → 4 days, team Network Team; raise SR; revert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New SR → Network Team, closure + 4 working days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team admin: create team, members; cannot deactivate a mapped team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /itsm-teams; PUT members; PATCH isActive=false on Desktop Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Created; members saved; deactivation blocked with reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category change re-routes to the new team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team member changes SR category to Hardware Request › Docking station with a reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team becomes Desktop Support; history shows the transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise a problem from repeated incidents and link them</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /problems; PATCH incidents problemId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRB-00001; GET /incidents?problemId lists the linked incidents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-priority problem gets Problem Manager approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /approvals/Problem/:id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Pending approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRB-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem cannot close while its approval is pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem approval still Pending; PATCH Closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve, then root cause → known error → closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problem Manager approves; PATCH Root Cause Identified (rootCause), Known Error (workaround), Closed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saved with history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise a change request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /changes Normal, risk Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-00001, status Pending Approval, approval Pending, L1 + L2 approvals created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cannot implement before approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH status In Progress while approvals pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approval cannot be bypassed by editing the field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH approvalStatus Approved directly, then In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 400/403 — only the approval workflow can approve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levels are approved in order (L1 before L2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve L2 while L1 pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approving all levels approves the change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve L1 then L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change approvalStatus = Approved; can move to In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approver name recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read approvals after action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approverName = the signed-in approver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejection stops the change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise change 2; reject L1; try to approve L2 and move to In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Rejected; further approvals blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Change Manager (non-admin) approves L1; others cannot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approve L1 as the Change Manager user; try as Asset Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Manager HTTP 200; Asset Manager HTTP 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approvers see a "My approvals" queue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise a change; GET /my-approvals as Change Manager and as the L2 approver; approve L1; check again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1 approver sees it first; after L1 it moves to the L2 approver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approvers are emailed; requester gets the decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check email_outbox after the changes above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approval-request emails to the Change Manager; decision emails to the requester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin override is allowed but recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base-role Admin (not a named approver) decides a Problem level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTTP 200; step flagged admin override; history says so</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APM-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raiser cannot approve own ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change Manager raises a change and tries L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHG-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard (pre-approved) change skips CAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise Standard change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No approvals or auto-approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise a service request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /service-requests (VPN access, Medium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-00001 Open; Line Manager approval Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fulfilment waits for approval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATCH status In Progress / Completed while approval Pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-priority request is auto-approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST Low priority SR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Approvals Auto-Approved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SR-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requester sees own requests (self-service)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GET /service-requests as an employee (Self-Service role, not in any team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only own requests; users without ITSM role get 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KB-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Knowledge Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publish a KB article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /knowledge-base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KB-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Article validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /knowledge-base without title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KB-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link KB article to incident resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Look for KB link on incident</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incident references KB article</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fail</t>
   </si>
   <si>
-    <t xml:space="preserve">No team / membership API — teams are only a list of names (itsm.itGroups); no members, no team lead, no queue</t>
+    <t xml:space="preserve">No link between incidents and KB articles</t>
   </si>
   <si>
     <t xml:space="preserve">Phase 3</t>
   </si>
   <si>
-    <t xml:space="preserve">CFG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only admin can change ITSM configuration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUT /itsm-config as IT Asset Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA Policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Create SLA policies per priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /sla-policies Critical 1h/4h, High 2h/8h, Medium 4h/24h, Low 8h/72h (Incident)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA policy validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /sla-policies with resolution time −5 and no name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only admin / ITSM admin can change SLA policies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /sla-policies as a user without ITSM rights (Asset Viewer)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APM-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approval Workflow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Configure approval matrix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /approval-matrix: Change L1 Change Manager, L2 CAB; Service Request L1 Line Manager; Incident L1 IT Head for Priority:Critical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rules created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APM-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approval matrix is admin-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /approval-matrix as IT Asset Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APM-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each level is linked to real approvers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read the rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change L1 → IT Hub role "Change Manager"; L2 → named person; label shows who</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incidents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log an incident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /incidents (High, Network, reporter, team Service Desk L1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 201; INC-00001; status Open; SLA due = created + 8h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mandatory fields enforced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /incidents without title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 400 with message</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invalid priority / status rejected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /incidents priority "Urgent!!"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Created-by is the signed-in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /incidents; read createdBy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">createdBy = signed-in user (not client supplied)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assign to a team member (ticket assignment)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH assignedTo = Desktop engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assignee saved; history records "assigned to …"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass ticket to another team (L1 → Network Team)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH assignedGroup Network Team, assignedTo cleared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group change recorded in history with who/when; new team notified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assignee must be a valid user / team member</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH assignedTo "Nobody Real", assignedGroup "Ghost Team"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status transitions follow the lifecycle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open → In Progress → Resolved (with notes) → Closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each step saved; resolvedAt / closedAt set; history rows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolve requires resolution notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH status Resolved without notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invalid jump blocked (Closed → In Progress without reopen reason)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH a Closed incident to In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 400 or reopen with reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P1/S1 incident is escalated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST Critical/S1 incident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status Escalated (or flag) + IT Head approval; notification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical incident gets IT Head approval step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GET /approvals/Incident/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Pending approval (L1 IT Head)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ticket numbers stay unique under parallel creation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 incidents created at the same moment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All HTTP 201, unique numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulk update records history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /incidents/bulk-update status In Progress for 2 tickets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">History row per ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles &amp; Access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service desk agent (non-admin, ITSM Incidents = Edit) logs and works an incident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign in as Service Desk Agent; POST /incidents; PATCH status In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 201 / 200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employee raises a service request / incident (self-service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sign in as employee with Self-Service role; POST /service-requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User without ITSM access cannot read tickets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GET /incidents as Asset Viewer (no ITSM permission)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITSM modules can be granted in Roles &amp; Permissions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check role modules list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITSM modules present (Incidents, Problems, Changes, KB, SLA, Service Requests, Approval Workflow)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delete needs a reason and is audited</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DELETE /incidents/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason required; audit entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audit trail names the person</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read audit_logs for the incident create</t>
-  </si>
-  <si>
-    <t xml:space="preserve">performedBy = signed-in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assignee / team is notified by email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assign an incident; check email_outbox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email logged for the assignment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No email / notification on assignment, escalation or resolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLA breach is detected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Back-date an open High incident by 10h; GET /incidents and /incidents/stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slaStatus "breached"; SLA Breached count ≥ 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INC-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First-response SLA is tracked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check incident fields for responded / first response time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">firstResponseAt + response SLA status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Response time in SLA policy is never measured (no first-response timestamp)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise a problem from repeated incidents and link them</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /problems; PATCH incidents problemId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRB-00001; GET /incidents?problemId lists the linked incidents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRB-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High-priority problem gets Problem Manager approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GET /approvals/Problem/:id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One Pending approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRB-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem cannot close while its approval is pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem approval still Pending; PATCH Closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRB-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve, then root cause → known error → closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Problem Manager approves; PATCH Root Cause Identified (rootCause), Known Error (workaround), Closed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saved with history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise a change request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /changes Normal, risk Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-00001, status Pending Approval, approval Pending, L1 + L2 approvals created</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cannot implement before approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH status In Progress while approvals pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approval cannot be bypassed by editing the field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH approvalStatus Approved directly, then In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 400/403 — only the approval workflow can approve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levels are approved in order (L1 before L2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve L2 while L1 pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approving all levels approves the change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve L1 then L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change approvalStatus = Approved; can move to In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approver name recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Read approvals after action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">approverName = the signed-in approver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rejection stops the change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise change 2; reject L1; try to approve L2 and move to In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Rejected; further approvals blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Change Manager (non-admin) approves L1; others cannot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approve L1 as the Change Manager user; try as Asset Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Manager HTTP 200; Asset Manager HTTP 403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approvers see a "My approvals" queue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise a change; GET /my-approvals as Change Manager and as the L2 approver; approve L1; check again</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1 approver sees it first; after L1 it moves to the L2 approver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APM-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approvers are emailed; requester gets the decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check email_outbox after the changes above</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approval-request emails to the Change Manager; decision emails to the requester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APM-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin override is allowed but recorded</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base-role Admin (not a named approver) decides a Problem level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP 200; step flagged admin override; history says so</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APM-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raiser cannot approve own ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Manager raises a change and tries L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHG-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard (pre-approved) change skips CAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise Standard change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No approvals or auto-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raise a service request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /service-requests (VPN access, Medium)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-00001 Open; Line Manager approval Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fulfilment waits for approval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PATCH status In Progress / Completed while approval Pending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low-priority request is auto-approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST Low priority SR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Approvals Auto-Approved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SR-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requester sees own requests (self-service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GET my service requests as a normal employee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only own tickets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every user sees every request (undefined rows) — no "my tickets" self-service view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KB-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Knowledge Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publish a KB article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /knowledge-base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KB-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Article validation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /knowledge-base without title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KB-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link KB article to incident resolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Look for KB link on incident</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incident references KB article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No link between incidents and KB articles</t>
-  </si>
-  <si>
     <t xml:space="preserve">ATT-01</t>
   </si>
   <si>
@@ -824,7 +947,7 @@
     <t xml:space="preserve">New count visible</t>
   </si>
   <si>
-    <t xml:space="preserve">ITSM — automated run after Phase 2</t>
+    <t xml:space="preserve">ITSM — automated run (category routing, teams, approvals)</t>
   </si>
   <si>
     <t xml:space="preserve">Total</t>
@@ -833,7 +956,7 @@
     <t xml:space="preserve">Passed</t>
   </si>
   <si>
-    <t xml:space="preserve">Open (Phase 3 scope)</t>
+    <t xml:space="preserve">Open</t>
   </si>
 </sst>
 </file>
@@ -1315,18 +1438,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
@@ -1412,7 +1534,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1434,15 +1556,13 @@
       <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>27</v>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -1450,7 +1570,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -1459,13 +1579,13 @@
         <v>16</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1484,22 +1604,22 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1518,22 +1638,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1552,22 +1672,22 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1586,25 +1706,25 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>21</v>
@@ -1620,25 +1740,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>21</v>
@@ -1654,25 +1774,25 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>21</v>
@@ -1688,25 +1808,25 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>21</v>
@@ -1722,25 +1842,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>21</v>
@@ -1756,25 +1876,25 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>21</v>
@@ -1790,25 +1910,25 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="G14" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>21</v>
@@ -1824,25 +1944,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="G15" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>21</v>
@@ -1858,25 +1978,25 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="G16" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>21</v>
@@ -1892,25 +2012,25 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>21</v>
@@ -1926,25 +2046,25 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>21</v>
@@ -1960,25 +2080,25 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>21</v>
@@ -1994,25 +2114,25 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>21</v>
@@ -2028,25 +2148,25 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>21</v>
@@ -2062,25 +2182,25 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>21</v>
@@ -2096,25 +2216,25 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>21</v>
@@ -2130,25 +2250,25 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>21</v>
@@ -2164,25 +2284,25 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>21</v>
@@ -2198,25 +2318,25 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>21</v>
@@ -2232,25 +2352,25 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -2266,25 +2386,25 @@
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>21</v>
@@ -2300,25 +2420,25 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>21</v>
@@ -2334,25 +2454,25 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>21</v>
@@ -2366,37 +2486,35 @@
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -2404,25 +2522,25 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>21</v>
@@ -2436,37 +2554,35 @@
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J33" s="2"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -2474,25 +2590,25 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>21</v>
@@ -2508,25 +2624,25 @@
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>21</v>
@@ -2542,31 +2658,31 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>42</v>
+        <v>158</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>22</v>
+        <v>159</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -2576,25 +2692,25 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="G37" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -2610,25 +2726,25 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -2642,27 +2758,27 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>21</v>
@@ -2676,27 +2792,27 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>21</v>
@@ -2710,27 +2826,27 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>21</v>
@@ -2746,25 +2862,25 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>21</v>
@@ -2778,27 +2894,27 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>21</v>
@@ -2814,25 +2930,25 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>21</v>
@@ -2848,25 +2964,25 @@
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>21</v>
@@ -2882,25 +2998,25 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>21</v>
@@ -2916,25 +3032,25 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
@@ -2950,25 +3066,25 @@
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>21</v>
@@ -2982,27 +3098,27 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -3018,25 +3134,25 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>216</v>
+        <v>39</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -3050,27 +3166,27 @@
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>21</v>
@@ -3084,27 +3200,27 @@
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
     </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>21</v>
@@ -3118,27 +3234,27 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>21</v>
@@ -3152,63 +3268,61 @@
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>232</v>
-      </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>21</v>
@@ -3222,27 +3336,27 @@
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="E56" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>42</v>
+        <v>237</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>21</v>
@@ -3256,37 +3370,35 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>27</v>
+        <v>48</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -3294,25 +3406,25 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>247</v>
+        <v>44</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>21</v>
@@ -3328,31 +3440,31 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>256</v>
+        <v>22</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
@@ -3362,25 +3474,25 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>261</v>
+        <v>30</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>21</v>
@@ -3396,25 +3508,25 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>21</v>
@@ -3428,8 +3540,384 @@
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
     </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N61"/>
+  <autoFilter ref="A1:N72"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3454,34 +3942,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="B3" s="7" t="n">
         <f aca="false">COUNTA('ITSM Test Cases'!A2:A200)</f>
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="B4" s="7" t="n">
         <f aca="false">COUNTIF('ITSM Test Cases'!H2:H200,"Pass")</f>
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="B5" s="7" t="n">
         <f aca="false">B3-B4</f>
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
